--- a/data/nzd0066/nzd0066.xlsx
+++ b/data/nzd0066/nzd0066.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P304"/>
+  <dimension ref="A1:P305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16822,6 +16822,60 @@
         <v>396.34</v>
       </c>
       <c r="P304" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>380.22</v>
+      </c>
+      <c r="C305" t="n">
+        <v>359.88</v>
+      </c>
+      <c r="D305" t="n">
+        <v>359.9</v>
+      </c>
+      <c r="E305" t="n">
+        <v>368.96</v>
+      </c>
+      <c r="F305" t="n">
+        <v>389.27</v>
+      </c>
+      <c r="G305" t="n">
+        <v>391.49</v>
+      </c>
+      <c r="H305" t="n">
+        <v>393.08</v>
+      </c>
+      <c r="I305" t="n">
+        <v>400.8</v>
+      </c>
+      <c r="J305" t="n">
+        <v>406.11</v>
+      </c>
+      <c r="K305" t="n">
+        <v>398.28</v>
+      </c>
+      <c r="L305" t="n">
+        <v>397.91</v>
+      </c>
+      <c r="M305" t="n">
+        <v>394.86</v>
+      </c>
+      <c r="N305" t="n">
+        <v>399.07</v>
+      </c>
+      <c r="O305" t="n">
+        <v>396.38</v>
+      </c>
+      <c r="P305" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16838,7 +16892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B307"/>
+  <dimension ref="A1:B308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19911,6 +19965,16 @@
       </c>
       <c r="B307" t="n">
         <v>0.24</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>1.15</v>
       </c>
     </row>
   </sheetData>
@@ -20079,28 +20143,28 @@
         <v>0.0103</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1532204544326598</v>
+        <v>0.1123839489273185</v>
       </c>
       <c r="J2" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K2" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0003879780549995715</v>
+        <v>0.0002095645670223689</v>
       </c>
       <c r="M2" t="n">
-        <v>40.64530414748683</v>
+        <v>40.60933465586744</v>
       </c>
       <c r="N2" t="n">
-        <v>2824.993229508776</v>
+        <v>2825.289584911181</v>
       </c>
       <c r="O2" t="n">
-        <v>53.15066537221126</v>
+        <v>53.15345317955533</v>
       </c>
       <c r="P2" t="n">
-        <v>430.4180081011964</v>
+        <v>430.8939129813087</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -20161,28 +20225,28 @@
         <v>0.09</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1939553372321006</v>
+        <v>-0.1972815745290899</v>
       </c>
       <c r="J3" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K3" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1162395804169256</v>
+        <v>0.119947548809731</v>
       </c>
       <c r="M3" t="n">
-        <v>3.039338014032117</v>
+        <v>3.04374426766684</v>
       </c>
       <c r="N3" t="n">
-        <v>14.97121591354027</v>
+        <v>15.00388130786538</v>
       </c>
       <c r="O3" t="n">
-        <v>3.869265552212754</v>
+        <v>3.873484388488661</v>
       </c>
       <c r="P3" t="n">
-        <v>369.9918721180636</v>
+        <v>370.0275652200976</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -20243,28 +20307,28 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.286544640689907</v>
+        <v>0.2799952295543519</v>
       </c>
       <c r="J4" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K4" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2405743448716775</v>
+        <v>0.2293618099242882</v>
       </c>
       <c r="M4" t="n">
-        <v>2.832566425008042</v>
+        <v>2.855367256333057</v>
       </c>
       <c r="N4" t="n">
-        <v>13.56730609577837</v>
+        <v>13.84025442794573</v>
       </c>
       <c r="O4" t="n">
-        <v>3.683382425947429</v>
+        <v>3.720249242718252</v>
       </c>
       <c r="P4" t="n">
-        <v>362.2453642812763</v>
+        <v>362.3156445346234</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -20325,28 +20389,28 @@
         <v>0.0935</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2106670235831835</v>
+        <v>0.205892022914611</v>
       </c>
       <c r="J5" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K5" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2723547368260503</v>
+        <v>0.2595300332748333</v>
       </c>
       <c r="M5" t="n">
-        <v>1.922768909382645</v>
+        <v>1.943152831761418</v>
       </c>
       <c r="N5" t="n">
-        <v>6.206560349030881</v>
+        <v>6.354951737690484</v>
       </c>
       <c r="O5" t="n">
-        <v>2.491296921089672</v>
+        <v>2.520902960784188</v>
       </c>
       <c r="P5" t="n">
-        <v>370.6278155934178</v>
+        <v>370.6790550483511</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -20407,28 +20471,28 @@
         <v>0.0818</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1200425271312535</v>
+        <v>0.1155905636943215</v>
       </c>
       <c r="J6" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K6" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07907202447900075</v>
+        <v>0.07309074468690047</v>
       </c>
       <c r="M6" t="n">
-        <v>2.010522185297155</v>
+        <v>2.027631076143713</v>
       </c>
       <c r="N6" t="n">
-        <v>8.785088832480083</v>
+        <v>8.902930533103634</v>
       </c>
       <c r="O6" t="n">
-        <v>2.963965052506538</v>
+        <v>2.983777896074645</v>
       </c>
       <c r="P6" t="n">
-        <v>392.8319153536523</v>
+        <v>392.87968836893</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -20489,28 +20553,28 @@
         <v>0.1274</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1133833870384422</v>
+        <v>0.1096466224620827</v>
       </c>
       <c r="J7" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K7" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07938481642681083</v>
+        <v>0.07420021321373027</v>
       </c>
       <c r="M7" t="n">
-        <v>2.071788541905956</v>
+        <v>2.083786601549121</v>
       </c>
       <c r="N7" t="n">
-        <v>7.803916814948136</v>
+        <v>7.88162611697109</v>
       </c>
       <c r="O7" t="n">
-        <v>2.793549143105976</v>
+        <v>2.807423394675461</v>
       </c>
       <c r="P7" t="n">
-        <v>394.1467304559719</v>
+        <v>394.1868288336258</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -20571,28 +20635,28 @@
         <v>0.1062</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3518912889764728</v>
+        <v>0.3465039755070298</v>
       </c>
       <c r="J8" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K8" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3102867221758093</v>
+        <v>0.3020793364730514</v>
       </c>
       <c r="M8" t="n">
-        <v>2.392906965547845</v>
+        <v>2.41452189536926</v>
       </c>
       <c r="N8" t="n">
-        <v>14.40772855303104</v>
+        <v>14.57521168656138</v>
       </c>
       <c r="O8" t="n">
-        <v>3.795751381878302</v>
+        <v>3.817749557862771</v>
       </c>
       <c r="P8" t="n">
-        <v>391.9503536926059</v>
+        <v>392.0081637380674</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -20653,28 +20717,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2610982816516625</v>
+        <v>0.2575290100287106</v>
       </c>
       <c r="J9" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K9" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1833843138376765</v>
+        <v>0.1794645601655258</v>
       </c>
       <c r="M9" t="n">
-        <v>2.862558714554631</v>
+        <v>2.874814081065218</v>
       </c>
       <c r="N9" t="n">
-        <v>15.89046663959239</v>
+        <v>15.93251554147501</v>
       </c>
       <c r="O9" t="n">
-        <v>3.986284816667317</v>
+        <v>3.99155552904817</v>
       </c>
       <c r="P9" t="n">
-        <v>399.3183674994632</v>
+        <v>399.3566685480207</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -20735,28 +20799,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1762449549037446</v>
+        <v>0.1749204569993561</v>
       </c>
       <c r="J10" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K10" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1022377844629991</v>
+        <v>0.1014212856357279</v>
       </c>
       <c r="M10" t="n">
-        <v>2.825114175846211</v>
+        <v>2.823219201506451</v>
       </c>
       <c r="N10" t="n">
-        <v>14.27763817364245</v>
+        <v>14.24366042800547</v>
       </c>
       <c r="O10" t="n">
-        <v>3.778576209849743</v>
+        <v>3.774077427399373</v>
       </c>
       <c r="P10" t="n">
-        <v>403.4700744599314</v>
+        <v>403.4842873481364</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -20817,28 +20881,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.04251737524711222</v>
+        <v>0.03968896429734362</v>
       </c>
       <c r="J11" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K11" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L11" t="n">
-        <v>0.007371286667543275</v>
+        <v>0.006444745355134063</v>
       </c>
       <c r="M11" t="n">
-        <v>2.612602317716422</v>
+        <v>2.617826010545157</v>
       </c>
       <c r="N11" t="n">
-        <v>12.74234956543461</v>
+        <v>12.7596623981383</v>
       </c>
       <c r="O11" t="n">
-        <v>3.569642778407191</v>
+        <v>3.572066964397266</v>
       </c>
       <c r="P11" t="n">
-        <v>401.4245014411609</v>
+        <v>401.4548524809728</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -20899,28 +20963,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1017518480615255</v>
+        <v>-0.1023590536570816</v>
       </c>
       <c r="J12" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K12" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04670351602005784</v>
+        <v>0.04754425535750584</v>
       </c>
       <c r="M12" t="n">
-        <v>2.411612300268914</v>
+        <v>2.407074474072072</v>
       </c>
       <c r="N12" t="n">
-        <v>11.06206270759842</v>
+        <v>11.02840405602423</v>
       </c>
       <c r="O12" t="n">
-        <v>3.325967935443519</v>
+        <v>3.320904102202324</v>
       </c>
       <c r="P12" t="n">
-        <v>401.4950667668791</v>
+        <v>401.5015825531393</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -20981,28 +21045,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1905301858396726</v>
+        <v>-0.1906635356247458</v>
       </c>
       <c r="J13" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K13" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1624712430580747</v>
+        <v>0.1636253968166477</v>
       </c>
       <c r="M13" t="n">
-        <v>2.233659292491345</v>
+        <v>2.227100635877763</v>
       </c>
       <c r="N13" t="n">
-        <v>9.795438829192577</v>
+        <v>9.763348643718517</v>
       </c>
       <c r="O13" t="n">
-        <v>3.12976657742915</v>
+        <v>3.124635761767844</v>
       </c>
       <c r="P13" t="n">
-        <v>400.0722039981447</v>
+        <v>400.0736349446046</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -21063,28 +21127,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2480396728637091</v>
+        <v>-0.245746839393181</v>
       </c>
       <c r="J14" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K14" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1840471149005793</v>
+        <v>0.1819192761329632</v>
       </c>
       <c r="M14" t="n">
-        <v>3.022078499579022</v>
+        <v>3.024661457773958</v>
       </c>
       <c r="N14" t="n">
-        <v>14.27747665023215</v>
+        <v>14.26943284270319</v>
       </c>
       <c r="O14" t="n">
-        <v>3.77855483620817</v>
+        <v>3.777490283601427</v>
       </c>
       <c r="P14" t="n">
-        <v>402.1283180257323</v>
+        <v>402.1037141470238</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -21145,28 +21209,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2417024070694422</v>
+        <v>-0.2408377529040933</v>
       </c>
       <c r="J15" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K15" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2648324543630953</v>
+        <v>0.2646865180730475</v>
       </c>
       <c r="M15" t="n">
-        <v>2.088078482926846</v>
+        <v>2.085965754165863</v>
       </c>
       <c r="N15" t="n">
-        <v>8.488875468071292</v>
+        <v>8.466486696762505</v>
       </c>
       <c r="O15" t="n">
-        <v>2.913567481296991</v>
+        <v>2.909722786927047</v>
       </c>
       <c r="P15" t="n">
-        <v>401.4288269457147</v>
+        <v>401.4195485369326</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -21208,7 +21272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P304"/>
+  <dimension ref="A1:P305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46043,6 +46107,88 @@
         </is>
       </c>
     </row>
+    <row r="305">
+      <c r="A305" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>-35.2729324825688,174.08036452096349</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>-35.27368583591826,174.08039986737174</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>-35.274403335241196,174.08058173922353</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>-35.27508016413273,174.0809318078084</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>-35.27564027960204,174.08146559458007</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>-35.27611003456355,174.08206075076527</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>-35.276561098758606,174.08273506713016</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>-35.276925406814144,174.0834774357734</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>-35.27723322554926,174.08423444012942</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>-35.27756789257008,174.0849884139819</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>-35.2778094740483,174.0858151344095</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>-35.27804550433166,174.08664722601713</t>
+        </is>
+      </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>-35.278178792818785,174.08751303505434</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>-35.27834904224479,174.08838006374634</t>
+        </is>
+      </c>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0066/nzd0066.xlsx
+++ b/data/nzd0066/nzd0066.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P305"/>
+  <dimension ref="A1:P307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16878,6 +16878,114 @@
       <c r="P305" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>398.38</v>
+      </c>
+      <c r="C306" t="n">
+        <v>361.83</v>
+      </c>
+      <c r="D306" t="n">
+        <v>362.12</v>
+      </c>
+      <c r="E306" t="n">
+        <v>368.05</v>
+      </c>
+      <c r="F306" t="n">
+        <v>389.12</v>
+      </c>
+      <c r="G306" t="n">
+        <v>391.04</v>
+      </c>
+      <c r="H306" t="n">
+        <v>392.64</v>
+      </c>
+      <c r="I306" t="n">
+        <v>400.51</v>
+      </c>
+      <c r="J306" t="n">
+        <v>404.58</v>
+      </c>
+      <c r="K306" t="n">
+        <v>397.55</v>
+      </c>
+      <c r="L306" t="n">
+        <v>396.86</v>
+      </c>
+      <c r="M306" t="n">
+        <v>394.54</v>
+      </c>
+      <c r="N306" t="n">
+        <v>396.91</v>
+      </c>
+      <c r="O306" t="n">
+        <v>396.15</v>
+      </c>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:11:57+00:00</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>398.38</v>
+      </c>
+      <c r="C307" t="n">
+        <v>362.3</v>
+      </c>
+      <c r="D307" t="n">
+        <v>363.44</v>
+      </c>
+      <c r="E307" t="n">
+        <v>369.56</v>
+      </c>
+      <c r="F307" t="n">
+        <v>390.33</v>
+      </c>
+      <c r="G307" t="n">
+        <v>390.38</v>
+      </c>
+      <c r="H307" t="n">
+        <v>391.94</v>
+      </c>
+      <c r="I307" t="n">
+        <v>400.51</v>
+      </c>
+      <c r="J307" t="n">
+        <v>402.34</v>
+      </c>
+      <c r="K307" t="n">
+        <v>395.82</v>
+      </c>
+      <c r="L307" t="n">
+        <v>394.9</v>
+      </c>
+      <c r="M307" t="n">
+        <v>393.29</v>
+      </c>
+      <c r="N307" t="n">
+        <v>396.91</v>
+      </c>
+      <c r="O307" t="n">
+        <v>396.15</v>
+      </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -16892,7 +17000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B308"/>
+  <dimension ref="A1:B310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19975,6 +20083,26 @@
       </c>
       <c r="B308" t="n">
         <v>1.15</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>-0.06</v>
       </c>
     </row>
   </sheetData>
@@ -20143,28 +20271,28 @@
         <v>0.0103</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1123839489273185</v>
+        <v>0.05958519535252409</v>
       </c>
       <c r="J2" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K2" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002095645670223689</v>
+        <v>5.962141803905752e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>40.60933465586744</v>
+        <v>40.46474208361054</v>
       </c>
       <c r="N2" t="n">
-        <v>2825.289584911181</v>
+        <v>2813.986794248319</v>
       </c>
       <c r="O2" t="n">
-        <v>53.15345317955533</v>
+        <v>53.04702436752055</v>
       </c>
       <c r="P2" t="n">
-        <v>430.8939129813087</v>
+        <v>431.5116962631297</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -20225,28 +20353,28 @@
         <v>0.09</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1972815745290899</v>
+        <v>-0.2008999819597541</v>
       </c>
       <c r="J3" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K3" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L3" t="n">
-        <v>0.119947548809731</v>
+        <v>0.1250173561785899</v>
       </c>
       <c r="M3" t="n">
-        <v>3.04374426766684</v>
+        <v>3.039253525876752</v>
       </c>
       <c r="N3" t="n">
-        <v>15.00388130786538</v>
+        <v>14.95495652150981</v>
       </c>
       <c r="O3" t="n">
-        <v>3.873484388488661</v>
+        <v>3.867163886042304</v>
       </c>
       <c r="P3" t="n">
-        <v>370.0275652200976</v>
+        <v>370.0665574103155</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -20307,28 +20435,28 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2799952295543519</v>
+        <v>0.2709168837948372</v>
       </c>
       <c r="J4" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K4" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2293618099242882</v>
+        <v>0.2165297870480648</v>
       </c>
       <c r="M4" t="n">
-        <v>2.855367256333057</v>
+        <v>2.881144983025433</v>
       </c>
       <c r="N4" t="n">
-        <v>13.84025442794573</v>
+        <v>14.05960809023288</v>
       </c>
       <c r="O4" t="n">
-        <v>3.720249242718252</v>
+        <v>3.749614392205268</v>
       </c>
       <c r="P4" t="n">
-        <v>362.3156445346234</v>
+        <v>362.4134729730335</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -20389,28 +20517,28 @@
         <v>0.0935</v>
       </c>
       <c r="I5" t="n">
-        <v>0.205892022914611</v>
+        <v>0.1963171833539113</v>
       </c>
       <c r="J5" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K5" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2595300332748333</v>
+        <v>0.2345546324222945</v>
       </c>
       <c r="M5" t="n">
-        <v>1.943152831761418</v>
+        <v>1.984119679180635</v>
       </c>
       <c r="N5" t="n">
-        <v>6.354951737690484</v>
+        <v>6.658601809633198</v>
       </c>
       <c r="O5" t="n">
-        <v>2.520902960784188</v>
+        <v>2.58042667201244</v>
       </c>
       <c r="P5" t="n">
-        <v>370.6790550483511</v>
+        <v>370.7822333201894</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -20471,28 +20599,28 @@
         <v>0.0818</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1155905636943215</v>
+        <v>0.1074626347489852</v>
       </c>
       <c r="J6" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K6" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07309074468690047</v>
+        <v>0.06299920211020871</v>
       </c>
       <c r="M6" t="n">
-        <v>2.027631076143713</v>
+        <v>2.057152790808938</v>
       </c>
       <c r="N6" t="n">
-        <v>8.902930533103634</v>
+        <v>9.093186770097159</v>
       </c>
       <c r="O6" t="n">
-        <v>2.983777896074645</v>
+        <v>3.015491132485247</v>
       </c>
       <c r="P6" t="n">
-        <v>392.87968836893</v>
+        <v>392.9672750059406</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -20553,28 +20681,28 @@
         <v>0.1274</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1096466224620827</v>
+        <v>0.1012967502521193</v>
       </c>
       <c r="J7" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K7" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07420021321373027</v>
+        <v>0.06292039692273388</v>
       </c>
       <c r="M7" t="n">
-        <v>2.083786601549121</v>
+        <v>2.112549684928719</v>
       </c>
       <c r="N7" t="n">
-        <v>7.88162611697109</v>
+        <v>8.090442730864568</v>
       </c>
       <c r="O7" t="n">
-        <v>2.807423394675461</v>
+        <v>2.844370357542169</v>
       </c>
       <c r="P7" t="n">
-        <v>394.1868288336258</v>
+        <v>394.2768135541475</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -20635,28 +20763,28 @@
         <v>0.1062</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3465039755070298</v>
+        <v>0.3348888010324179</v>
       </c>
       <c r="J8" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K8" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3020793364730514</v>
+        <v>0.2838079674998553</v>
       </c>
       <c r="M8" t="n">
-        <v>2.41452189536926</v>
+        <v>2.466682416871073</v>
       </c>
       <c r="N8" t="n">
-        <v>14.57521168656138</v>
+        <v>14.98312429038677</v>
       </c>
       <c r="O8" t="n">
-        <v>3.817749557862771</v>
+        <v>3.870804088349961</v>
       </c>
       <c r="P8" t="n">
-        <v>392.0081637380674</v>
+        <v>392.1333371508638</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -20717,28 +20845,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2575290100287106</v>
+        <v>0.2501279116578218</v>
       </c>
       <c r="J9" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K9" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1794645601655258</v>
+        <v>0.1712225238933019</v>
       </c>
       <c r="M9" t="n">
-        <v>2.874814081065218</v>
+        <v>2.902083485656234</v>
       </c>
       <c r="N9" t="n">
-        <v>15.93251554147501</v>
+        <v>16.03236496414844</v>
       </c>
       <c r="O9" t="n">
-        <v>3.99155552904817</v>
+        <v>4.004043576704484</v>
       </c>
       <c r="P9" t="n">
-        <v>399.3566685480207</v>
+        <v>399.4364265771147</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -20799,28 +20927,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1749204569993561</v>
+        <v>0.1688375704422648</v>
       </c>
       <c r="J10" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K10" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1014212856357279</v>
+        <v>0.09548178889859071</v>
       </c>
       <c r="M10" t="n">
-        <v>2.823219201506451</v>
+        <v>2.838508243135708</v>
       </c>
       <c r="N10" t="n">
-        <v>14.24366042800547</v>
+        <v>14.29654801965198</v>
       </c>
       <c r="O10" t="n">
-        <v>3.774077427399373</v>
+        <v>3.781077626768853</v>
       </c>
       <c r="P10" t="n">
-        <v>403.4842873481364</v>
+        <v>403.5498472100725</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -20881,28 +21009,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.03968896429734362</v>
+        <v>0.0320647975196002</v>
       </c>
       <c r="J11" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K11" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L11" t="n">
-        <v>0.006444745355134063</v>
+        <v>0.004202586093436378</v>
       </c>
       <c r="M11" t="n">
-        <v>2.617826010545157</v>
+        <v>2.638277873359794</v>
       </c>
       <c r="N11" t="n">
-        <v>12.7596623981383</v>
+        <v>12.89756157061854</v>
       </c>
       <c r="O11" t="n">
-        <v>3.572066964397266</v>
+        <v>3.59131752573043</v>
       </c>
       <c r="P11" t="n">
-        <v>401.4548524809728</v>
+        <v>401.5370202208499</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -20963,28 +21091,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1023590536570816</v>
+        <v>-0.1061938195394138</v>
       </c>
       <c r="J12" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K12" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04754425535750584</v>
+        <v>0.05140453777409093</v>
       </c>
       <c r="M12" t="n">
-        <v>2.407074474072072</v>
+        <v>2.412564184248073</v>
       </c>
       <c r="N12" t="n">
-        <v>11.02840405602423</v>
+        <v>11.01727776403563</v>
       </c>
       <c r="O12" t="n">
-        <v>3.320904102202324</v>
+        <v>3.319228489278138</v>
       </c>
       <c r="P12" t="n">
-        <v>401.5015825531393</v>
+        <v>401.5429145243857</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -21045,28 +21173,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1906635356247458</v>
+        <v>-0.1921481889291305</v>
       </c>
       <c r="J13" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K13" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1636253968166477</v>
+        <v>0.1675664730245255</v>
       </c>
       <c r="M13" t="n">
-        <v>2.227100635877763</v>
+        <v>2.221213319415603</v>
       </c>
       <c r="N13" t="n">
-        <v>9.763348643718517</v>
+        <v>9.710268903860749</v>
       </c>
       <c r="O13" t="n">
-        <v>3.124635761767844</v>
+        <v>3.116130437555647</v>
       </c>
       <c r="P13" t="n">
-        <v>400.0736349446046</v>
+        <v>400.089638521544</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -21127,28 +21255,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.245746839393181</v>
+        <v>-0.2440581688726671</v>
       </c>
       <c r="J14" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K14" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1819192761329632</v>
+        <v>0.1818563325409043</v>
       </c>
       <c r="M14" t="n">
-        <v>3.024661457773958</v>
+        <v>3.014078442773345</v>
       </c>
       <c r="N14" t="n">
-        <v>14.26943284270319</v>
+        <v>14.18678780437519</v>
       </c>
       <c r="O14" t="n">
-        <v>3.777490283601427</v>
+        <v>3.766535251975639</v>
       </c>
       <c r="P14" t="n">
-        <v>402.1037141470238</v>
+        <v>402.0855161549854</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -21209,28 +21337,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2408377529040933</v>
+        <v>-0.2394117722604625</v>
       </c>
       <c r="J15" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K15" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2646865180730475</v>
+        <v>0.2649473077036194</v>
       </c>
       <c r="M15" t="n">
-        <v>2.085965754165863</v>
+        <v>2.08022521521738</v>
       </c>
       <c r="N15" t="n">
-        <v>8.466486696762505</v>
+        <v>8.418722533719327</v>
       </c>
       <c r="O15" t="n">
-        <v>2.909722786927047</v>
+        <v>2.901503495382924</v>
       </c>
       <c r="P15" t="n">
-        <v>401.4195485369326</v>
+        <v>401.4041814252093</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -21272,7 +21400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P305"/>
+  <dimension ref="A1:P307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46189,6 +46317,170 @@
         </is>
       </c>
     </row>
+    <row r="306">
+      <c r="A306" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>-35.27288573838847,174.0805558630094</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>-35.2736814864705,174.0804206395175</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>-35.27439832600734,174.0806053696889</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>-35.27508300973161,174.08092242400775</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>-35.2756410350478,174.08146422670515</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>-35.27611300600274,174.08205738208343</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>-35.27656421598035,174.08273207508054</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>-35.27692759570193,174.08347569189172</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>-35.27724559760238,174.08422700063574</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>-35.27757404768892,174.0849855716819</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>-35.27781848691794,174.0858116027078</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>-35.27804829182317,174.08664631859347</t>
+        </is>
+      </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>-35.27819782244173,174.08750798829917</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>-35.278351076233726,174.0883795714358</t>
+        </is>
+      </c>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:11:57+00:00</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>-35.27288573838847,174.0805558630094</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>-35.27368043814155,174.0804256461369</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>-35.2743953475418,174.08061942023446</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>-35.27507828791329,174.08093799492934</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>-35.27563494111825,174.08147526089542</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>-35.2761173641134,174.0820524413496</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>-35.27656917519662,174.08272731500122</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>-35.27692759570193,174.08347569189172</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>-35.277263710934264,174.084216108824</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>-35.27758863447716,174.0849788358186</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>-35.27783531094097,174.0858050101959</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>-35.2780591804618,174.0866427739692</t>
+        </is>
+      </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>-35.27819782244173,174.08750798829917</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>-35.278351076233726,174.0883795714358</t>
+        </is>
+      </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0066/nzd0066.xlsx
+++ b/data/nzd0066/nzd0066.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P307"/>
+  <dimension ref="A1:P308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16942,7 +16942,7 @@
         </is>
       </c>
       <c r="B307" t="n">
-        <v>398.38</v>
+        <v>384.52</v>
       </c>
       <c r="C307" t="n">
         <v>362.3</v>
@@ -16984,6 +16984,60 @@
         <v>396.15</v>
       </c>
       <c r="P307" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>381.67</v>
+      </c>
+      <c r="C308" t="n">
+        <v>365.3</v>
+      </c>
+      <c r="D308" t="n">
+        <v>367.28</v>
+      </c>
+      <c r="E308" t="n">
+        <v>372.44</v>
+      </c>
+      <c r="F308" t="n">
+        <v>395.34</v>
+      </c>
+      <c r="G308" t="n">
+        <v>393.16</v>
+      </c>
+      <c r="H308" t="n">
+        <v>395.1</v>
+      </c>
+      <c r="I308" t="n">
+        <v>399.19</v>
+      </c>
+      <c r="J308" t="n">
+        <v>399.56</v>
+      </c>
+      <c r="K308" t="n">
+        <v>391.69</v>
+      </c>
+      <c r="L308" t="n">
+        <v>393.26</v>
+      </c>
+      <c r="M308" t="n">
+        <v>391.84</v>
+      </c>
+      <c r="N308" t="n">
+        <v>393.41</v>
+      </c>
+      <c r="O308" t="n">
+        <v>395.57</v>
+      </c>
+      <c r="P308" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -17000,7 +17054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B310"/>
+  <dimension ref="A1:B311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20103,6 +20157,16 @@
       </c>
       <c r="B310" t="n">
         <v>-0.06</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>0.13</v>
       </c>
     </row>
   </sheetData>
@@ -20271,28 +20335,28 @@
         <v>0.0103</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05958519535252409</v>
+        <v>0.01033544831427748</v>
       </c>
       <c r="J2" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K2" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L2" t="n">
-        <v>5.962141803905752e-05</v>
+        <v>1.799482668873864e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>40.46474208361054</v>
+        <v>40.45174573287112</v>
       </c>
       <c r="N2" t="n">
-        <v>2813.986794248319</v>
+        <v>2817.300448372145</v>
       </c>
       <c r="O2" t="n">
-        <v>53.04702436752055</v>
+        <v>53.07824835440734</v>
       </c>
       <c r="P2" t="n">
-        <v>431.5116962631297</v>
+        <v>432.0937667782177</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -20353,28 +20417,28 @@
         <v>0.09</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2008999819597541</v>
+        <v>-0.2004986609657331</v>
       </c>
       <c r="J3" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K3" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1250173561785899</v>
+        <v>0.1253740891713967</v>
       </c>
       <c r="M3" t="n">
-        <v>3.039253525876752</v>
+        <v>3.031581115505001</v>
       </c>
       <c r="N3" t="n">
-        <v>14.95495652150981</v>
+        <v>14.90740633004531</v>
       </c>
       <c r="O3" t="n">
-        <v>3.867163886042304</v>
+        <v>3.861011050236105</v>
       </c>
       <c r="P3" t="n">
-        <v>370.0665574103155</v>
+        <v>370.062174486719</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -20435,28 +20499,28 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2709168837948372</v>
+        <v>0.269337886113734</v>
       </c>
       <c r="J4" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K4" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2165297870480648</v>
+        <v>0.2155744767864374</v>
       </c>
       <c r="M4" t="n">
-        <v>2.881144983025433</v>
+        <v>2.879249843071087</v>
       </c>
       <c r="N4" t="n">
-        <v>14.05960809023288</v>
+        <v>14.03181524397476</v>
       </c>
       <c r="O4" t="n">
-        <v>3.749614392205268</v>
+        <v>3.745906464926047</v>
       </c>
       <c r="P4" t="n">
-        <v>362.4134729730335</v>
+        <v>362.4307175884372</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -20517,28 +20581,28 @@
         <v>0.0935</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1963171833539113</v>
+        <v>0.1939206907033355</v>
       </c>
       <c r="J5" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K5" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2345546324222945</v>
+        <v>0.2303689879077685</v>
       </c>
       <c r="M5" t="n">
-        <v>1.984119679180635</v>
+        <v>1.991174342858831</v>
       </c>
       <c r="N5" t="n">
-        <v>6.658601809633198</v>
+        <v>6.678384684690306</v>
       </c>
       <c r="O5" t="n">
-        <v>2.58042667201244</v>
+        <v>2.584257085641888</v>
       </c>
       <c r="P5" t="n">
-        <v>370.7822333201894</v>
+        <v>370.808405995787</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -20599,28 +20663,28 @@
         <v>0.0818</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1074626347489852</v>
+        <v>0.1071326200091993</v>
       </c>
       <c r="J6" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K6" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06299920211020871</v>
+        <v>0.06306394665786774</v>
       </c>
       <c r="M6" t="n">
-        <v>2.057152790808938</v>
+        <v>2.052131532924363</v>
       </c>
       <c r="N6" t="n">
-        <v>9.093186770097159</v>
+        <v>9.064353718701829</v>
       </c>
       <c r="O6" t="n">
-        <v>3.015491132485247</v>
+        <v>3.010706514873515</v>
       </c>
       <c r="P6" t="n">
-        <v>392.9672750059406</v>
+        <v>392.970879176696</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -20681,28 +20745,28 @@
         <v>0.1274</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1012967502521193</v>
+        <v>0.09874209207177875</v>
       </c>
       <c r="J7" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K7" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06292039692273388</v>
+        <v>0.06005974621777843</v>
       </c>
       <c r="M7" t="n">
-        <v>2.112549684928719</v>
+        <v>2.118696879364584</v>
       </c>
       <c r="N7" t="n">
-        <v>8.090442730864568</v>
+        <v>8.111216492840759</v>
       </c>
       <c r="O7" t="n">
-        <v>2.844370357542169</v>
+        <v>2.848019749376882</v>
       </c>
       <c r="P7" t="n">
-        <v>394.2768135541475</v>
+        <v>394.3047135937328</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -20763,28 +20827,28 @@
         <v>0.1062</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3348888010324179</v>
+        <v>0.330895556067722</v>
       </c>
       <c r="J8" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K8" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2838079674998553</v>
+        <v>0.2788871785859753</v>
       </c>
       <c r="M8" t="n">
-        <v>2.466682416871073</v>
+        <v>2.482595256644917</v>
       </c>
       <c r="N8" t="n">
-        <v>14.98312429038677</v>
+        <v>15.04946723593885</v>
       </c>
       <c r="O8" t="n">
-        <v>3.870804088349961</v>
+        <v>3.879364282448717</v>
       </c>
       <c r="P8" t="n">
-        <v>392.1333371508638</v>
+        <v>392.1769483445045</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -20845,28 +20909,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2501279116578218</v>
+        <v>0.2455016526052026</v>
       </c>
       <c r="J9" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K9" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1712225238933019</v>
+        <v>0.165672156576956</v>
       </c>
       <c r="M9" t="n">
-        <v>2.902083485656234</v>
+        <v>2.920974243931883</v>
       </c>
       <c r="N9" t="n">
-        <v>16.03236496414844</v>
+        <v>16.13469051304334</v>
       </c>
       <c r="O9" t="n">
-        <v>4.004043576704484</v>
+        <v>4.016801029805103</v>
       </c>
       <c r="P9" t="n">
-        <v>399.4364265771147</v>
+        <v>399.486951070643</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -20927,28 +20991,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1688375704422648</v>
+        <v>0.1631587484530134</v>
       </c>
       <c r="J10" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K10" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L10" t="n">
-        <v>0.09548178889859071</v>
+        <v>0.08901111954473639</v>
       </c>
       <c r="M10" t="n">
-        <v>2.838508243135708</v>
+        <v>2.860262531929657</v>
       </c>
       <c r="N10" t="n">
-        <v>14.29654801965198</v>
+        <v>14.48285327939941</v>
       </c>
       <c r="O10" t="n">
-        <v>3.781077626768853</v>
+        <v>3.805634412210322</v>
       </c>
       <c r="P10" t="n">
-        <v>403.5498472100725</v>
+        <v>403.6118669978926</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -21009,28 +21073,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0320647975196002</v>
+        <v>0.0249109209556901</v>
       </c>
       <c r="J11" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K11" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L11" t="n">
-        <v>0.004202586093436378</v>
+        <v>0.002488071764447319</v>
       </c>
       <c r="M11" t="n">
-        <v>2.638277873359794</v>
+        <v>2.66477998029607</v>
       </c>
       <c r="N11" t="n">
-        <v>12.89756157061854</v>
+        <v>13.22511174200766</v>
       </c>
       <c r="O11" t="n">
-        <v>3.59131752573043</v>
+        <v>3.636634672607033</v>
       </c>
       <c r="P11" t="n">
-        <v>401.5370202208499</v>
+        <v>401.6151494362796</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -21091,28 +21155,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1061938195394138</v>
+        <v>-0.1098332385073934</v>
       </c>
       <c r="J12" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K12" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05140453777409093</v>
+        <v>0.05472273148773665</v>
       </c>
       <c r="M12" t="n">
-        <v>2.412564184248073</v>
+        <v>2.424743462856159</v>
       </c>
       <c r="N12" t="n">
-        <v>11.01727776403563</v>
+        <v>11.07703718579098</v>
       </c>
       <c r="O12" t="n">
-        <v>3.319228489278138</v>
+        <v>3.328218320031151</v>
       </c>
       <c r="P12" t="n">
-        <v>401.5429145243857</v>
+        <v>401.5826614987776</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -21173,28 +21237,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1921481889291305</v>
+        <v>-0.1942321761242609</v>
       </c>
       <c r="J13" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K13" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1675664730245255</v>
+        <v>0.1711783273131133</v>
       </c>
       <c r="M13" t="n">
-        <v>2.221213319415603</v>
+        <v>2.225924921637084</v>
       </c>
       <c r="N13" t="n">
-        <v>9.710268903860749</v>
+        <v>9.710000677334346</v>
       </c>
       <c r="O13" t="n">
-        <v>3.116130437555647</v>
+        <v>3.116087398860043</v>
       </c>
       <c r="P13" t="n">
-        <v>400.089638521544</v>
+        <v>400.1123982495133</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -21255,28 +21319,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2440581688726671</v>
+        <v>-0.2454985108425469</v>
       </c>
       <c r="J14" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K14" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1818563325409043</v>
+        <v>0.1845564518742538</v>
       </c>
       <c r="M14" t="n">
-        <v>3.014078442773345</v>
+        <v>3.010543897023421</v>
       </c>
       <c r="N14" t="n">
-        <v>14.18678780437519</v>
+        <v>14.15555758236408</v>
       </c>
       <c r="O14" t="n">
-        <v>3.766535251975639</v>
+        <v>3.762387218557398</v>
       </c>
       <c r="P14" t="n">
-        <v>402.0855161549854</v>
+        <v>402.1012464778463</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -21337,28 +21401,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2394117722604625</v>
+        <v>-0.239041212502857</v>
       </c>
       <c r="J15" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K15" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2649473077036194</v>
+        <v>0.2657501226957037</v>
       </c>
       <c r="M15" t="n">
-        <v>2.08022521521738</v>
+        <v>2.075463614417169</v>
       </c>
       <c r="N15" t="n">
-        <v>8.418722533719327</v>
+        <v>8.392291548551558</v>
       </c>
       <c r="O15" t="n">
-        <v>2.901503495382924</v>
+        <v>2.896945209794545</v>
       </c>
       <c r="P15" t="n">
-        <v>401.4041814252093</v>
+        <v>401.4001344525124</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -21400,7 +21464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P307"/>
+  <dimension ref="A1:P308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46407,7 +46471,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>-35.27288573838847,174.0805558630094</t>
+          <t>-35.27292141431524,174.080409827746</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -46476,6 +46540,88 @@
         </is>
       </c>
       <c r="P307" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>-35.27292875025261,174.0803797988334</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>-35.27367374667526,174.0804576032789</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>-35.2743866829056,174.0806602945427</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>-35.27506928205563,174.0809676931058</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>-35.27560970921765,174.08152094789685</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>-35.276099007221724,174.0820732523158</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>-35.276546787876036,174.08274880335483</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>-35.27693755891498,174.08346775422223</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>-35.27728619087163,174.08420259130096</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>-35.27762345727069,174.08496275539548</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>-35.27784938818445,174.08579949401047</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>-35.278071811282494,174.0866386622039</t>
+        </is>
+      </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>-35.27822865747841,174.08749981068186</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>-35.27835620542321,174.08837832995698</t>
+        </is>
+      </c>
+      <c r="P308" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0066/nzd0066.xlsx
+++ b/data/nzd0066/nzd0066.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P308"/>
+  <dimension ref="A1:P310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16780,7 +16780,7 @@
         </is>
       </c>
       <c r="B304" t="n">
-        <v>401.85</v>
+        <v>412.66</v>
       </c>
       <c r="C304" t="n">
         <v>360.22</v>
@@ -16833,9 +16833,7 @@
           <t>2025-12-07 22:11:45+00:00</t>
         </is>
       </c>
-      <c r="B305" t="n">
-        <v>380.22</v>
-      </c>
+      <c r="B305" t="inlineStr"/>
       <c r="C305" t="n">
         <v>359.88</v>
       </c>
@@ -16888,7 +16886,7 @@
         </is>
       </c>
       <c r="B306" t="n">
-        <v>398.38</v>
+        <v>416.53</v>
       </c>
       <c r="C306" t="n">
         <v>361.83</v>
@@ -16942,7 +16940,7 @@
         </is>
       </c>
       <c r="B307" t="n">
-        <v>384.52</v>
+        <v>416.53</v>
       </c>
       <c r="C307" t="n">
         <v>362.3</v>
@@ -16996,7 +16994,7 @@
         </is>
       </c>
       <c r="B308" t="n">
-        <v>381.67</v>
+        <v>416.53</v>
       </c>
       <c r="C308" t="n">
         <v>365.3</v>
@@ -17040,6 +17038,114 @@
       <c r="P308" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>416.53</v>
+      </c>
+      <c r="C309" t="n">
+        <v>363.5</v>
+      </c>
+      <c r="D309" t="n">
+        <v>366.07</v>
+      </c>
+      <c r="E309" t="n">
+        <v>373.98</v>
+      </c>
+      <c r="F309" t="n">
+        <v>393.84</v>
+      </c>
+      <c r="G309" t="n">
+        <v>393.69</v>
+      </c>
+      <c r="H309" t="n">
+        <v>395.34</v>
+      </c>
+      <c r="I309" t="n">
+        <v>402.09</v>
+      </c>
+      <c r="J309" t="n">
+        <v>401.95</v>
+      </c>
+      <c r="K309" t="n">
+        <v>395.94</v>
+      </c>
+      <c r="L309" t="n">
+        <v>394.18</v>
+      </c>
+      <c r="M309" t="n">
+        <v>392.88</v>
+      </c>
+      <c r="N309" t="n">
+        <v>397.27</v>
+      </c>
+      <c r="O309" t="n">
+        <v>396.33</v>
+      </c>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>429.11</v>
+      </c>
+      <c r="C310" t="n">
+        <v>363.5</v>
+      </c>
+      <c r="D310" t="n">
+        <v>366.07</v>
+      </c>
+      <c r="E310" t="n">
+        <v>375.16</v>
+      </c>
+      <c r="F310" t="n">
+        <v>394.2</v>
+      </c>
+      <c r="G310" t="n">
+        <v>394.06</v>
+      </c>
+      <c r="H310" t="n">
+        <v>397</v>
+      </c>
+      <c r="I310" t="n">
+        <v>402.39</v>
+      </c>
+      <c r="J310" t="n">
+        <v>401.95</v>
+      </c>
+      <c r="K310" t="n">
+        <v>395.94</v>
+      </c>
+      <c r="L310" t="n">
+        <v>394.18</v>
+      </c>
+      <c r="M310" t="n">
+        <v>392.88</v>
+      </c>
+      <c r="N310" t="n">
+        <v>398.57</v>
+      </c>
+      <c r="O310" t="n">
+        <v>397.15</v>
+      </c>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -17054,7 +17160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B311"/>
+  <dimension ref="A1:B313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20167,6 +20273,26 @@
       </c>
       <c r="B311" t="n">
         <v>0.13</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>0.87</v>
       </c>
     </row>
   </sheetData>
@@ -20335,28 +20461,28 @@
         <v>0.0103</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01033544831427748</v>
+        <v>0.1036830328548805</v>
       </c>
       <c r="J2" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K2" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L2" t="n">
-        <v>1.799482668873864e-06</v>
+        <v>0.0001845774866634509</v>
       </c>
       <c r="M2" t="n">
-        <v>40.45174573287112</v>
+        <v>40.0554977741487</v>
       </c>
       <c r="N2" t="n">
-        <v>2817.300448372145</v>
+        <v>2777.661383937539</v>
       </c>
       <c r="O2" t="n">
-        <v>53.07824835440734</v>
+        <v>52.70352344898336</v>
       </c>
       <c r="P2" t="n">
-        <v>432.0937667782177</v>
+        <v>431.0034985793014</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -20417,28 +20543,28 @@
         <v>0.09</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2004986609657331</v>
+        <v>-0.2020717634823941</v>
       </c>
       <c r="J3" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K3" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1253740891713967</v>
+        <v>0.1286618597404877</v>
       </c>
       <c r="M3" t="n">
-        <v>3.031581115505001</v>
+        <v>3.018456686199517</v>
       </c>
       <c r="N3" t="n">
-        <v>14.90740633004531</v>
+        <v>14.81991799892339</v>
       </c>
       <c r="O3" t="n">
-        <v>3.861011050236105</v>
+        <v>3.849664660580632</v>
       </c>
       <c r="P3" t="n">
-        <v>370.062174486719</v>
+        <v>370.0794234222641</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -20499,28 +20625,28 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.269337886113734</v>
+        <v>0.2646108134257596</v>
       </c>
       <c r="J4" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K4" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2155744767864374</v>
+        <v>0.2111109587696075</v>
       </c>
       <c r="M4" t="n">
-        <v>2.879249843071087</v>
+        <v>2.883358829008453</v>
       </c>
       <c r="N4" t="n">
-        <v>14.03181524397476</v>
+        <v>14.02225815483302</v>
       </c>
       <c r="O4" t="n">
-        <v>3.745906464926047</v>
+        <v>3.744630576549977</v>
       </c>
       <c r="P4" t="n">
-        <v>362.4307175884372</v>
+        <v>362.4825496010701</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -20581,28 +20707,28 @@
         <v>0.0935</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1939206907033355</v>
+        <v>0.1920267150173312</v>
       </c>
       <c r="J5" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K5" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2303689879077685</v>
+        <v>0.2290762523227162</v>
       </c>
       <c r="M5" t="n">
-        <v>1.991174342858831</v>
+        <v>1.989098320356663</v>
       </c>
       <c r="N5" t="n">
-        <v>6.678384684690306</v>
+        <v>6.650469365377956</v>
       </c>
       <c r="O5" t="n">
-        <v>2.584257085641888</v>
+        <v>2.578850396083099</v>
       </c>
       <c r="P5" t="n">
-        <v>370.808405995787</v>
+        <v>370.8291694684598</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -20663,28 +20789,28 @@
         <v>0.0818</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1071326200091993</v>
+        <v>0.1047252959763318</v>
       </c>
       <c r="J6" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K6" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06306394665786774</v>
+        <v>0.06113132721796199</v>
       </c>
       <c r="M6" t="n">
-        <v>2.052131532924363</v>
+        <v>2.050910500374187</v>
       </c>
       <c r="N6" t="n">
-        <v>9.064353718701829</v>
+        <v>9.026966982079129</v>
       </c>
       <c r="O6" t="n">
-        <v>3.010706514873515</v>
+        <v>3.004491135297145</v>
       </c>
       <c r="P6" t="n">
-        <v>392.970879176696</v>
+        <v>392.9972741553815</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -20745,28 +20871,28 @@
         <v>0.1274</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09874209207177875</v>
+        <v>0.09468308044184275</v>
       </c>
       <c r="J7" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K7" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06005974621777843</v>
+        <v>0.05587000307505807</v>
       </c>
       <c r="M7" t="n">
-        <v>2.118696879364584</v>
+        <v>2.125570117862889</v>
       </c>
       <c r="N7" t="n">
-        <v>8.111216492840759</v>
+        <v>8.118868299481415</v>
       </c>
       <c r="O7" t="n">
-        <v>2.848019749376882</v>
+        <v>2.84936278832328</v>
       </c>
       <c r="P7" t="n">
-        <v>394.3047135937328</v>
+        <v>394.3492191345807</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -20827,28 +20953,28 @@
         <v>0.1062</v>
       </c>
       <c r="I8" t="n">
-        <v>0.330895556067722</v>
+        <v>0.3244576547065957</v>
       </c>
       <c r="J8" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K8" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2788871785859753</v>
+        <v>0.2719042299325125</v>
       </c>
       <c r="M8" t="n">
-        <v>2.482595256644917</v>
+        <v>2.505609742681638</v>
       </c>
       <c r="N8" t="n">
-        <v>15.04946723593885</v>
+        <v>15.10727834934646</v>
       </c>
       <c r="O8" t="n">
-        <v>3.879364282448717</v>
+        <v>3.886808247051359</v>
       </c>
       <c r="P8" t="n">
-        <v>392.1769483445045</v>
+        <v>392.2475340757238</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -20909,28 +21035,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2455016526052026</v>
+        <v>0.2404573462729928</v>
       </c>
       <c r="J9" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K9" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="L9" t="n">
-        <v>0.165672156576956</v>
+        <v>0.1612071030045904</v>
       </c>
       <c r="M9" t="n">
-        <v>2.920974243931883</v>
+        <v>2.932805439901857</v>
       </c>
       <c r="N9" t="n">
-        <v>16.13469051304334</v>
+        <v>16.12294260743721</v>
       </c>
       <c r="O9" t="n">
-        <v>4.016801029805103</v>
+        <v>4.015338417548041</v>
       </c>
       <c r="P9" t="n">
-        <v>399.486951070643</v>
+        <v>399.5422605548968</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -20991,28 +21117,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1631587484530134</v>
+        <v>0.155186643318459</v>
       </c>
       <c r="J10" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K10" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="L10" t="n">
-        <v>0.08901111954473639</v>
+        <v>0.08111700436694991</v>
       </c>
       <c r="M10" t="n">
-        <v>2.860262531929657</v>
+        <v>2.88662645326254</v>
       </c>
       <c r="N10" t="n">
-        <v>14.48285327939941</v>
+        <v>14.6202442281251</v>
       </c>
       <c r="O10" t="n">
-        <v>3.805634412210322</v>
+        <v>3.823642795571404</v>
       </c>
       <c r="P10" t="n">
-        <v>403.6118669978926</v>
+        <v>403.6992805376453</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -21073,28 +21199,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0249109209556901</v>
+        <v>0.01653157267826132</v>
       </c>
       <c r="J11" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K11" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="L11" t="n">
-        <v>0.002488071764447319</v>
+        <v>0.001092227663263334</v>
       </c>
       <c r="M11" t="n">
-        <v>2.66477998029607</v>
+        <v>2.689343632952715</v>
       </c>
       <c r="N11" t="n">
-        <v>13.22511174200766</v>
+        <v>13.39486064151662</v>
       </c>
       <c r="O11" t="n">
-        <v>3.636634672607033</v>
+        <v>3.659898993348945</v>
       </c>
       <c r="P11" t="n">
-        <v>401.6151494362796</v>
+        <v>401.7070283563884</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -21155,28 +21281,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1098332385073934</v>
+        <v>-0.1157165235334523</v>
       </c>
       <c r="J12" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K12" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05472273148773665</v>
+        <v>0.06056377416792658</v>
       </c>
       <c r="M12" t="n">
-        <v>2.424743462856159</v>
+        <v>2.441904844053504</v>
       </c>
       <c r="N12" t="n">
-        <v>11.07703718579098</v>
+        <v>11.13121996011918</v>
       </c>
       <c r="O12" t="n">
-        <v>3.328218320031151</v>
+        <v>3.336348297183491</v>
       </c>
       <c r="P12" t="n">
-        <v>401.5826614987776</v>
+        <v>401.6471712650765</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -21237,28 +21363,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1942321761242609</v>
+        <v>-0.1969050893128351</v>
       </c>
       <c r="J13" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K13" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1711783273131133</v>
+        <v>0.1768225724863752</v>
       </c>
       <c r="M13" t="n">
-        <v>2.225924921637084</v>
+        <v>2.226625042341362</v>
       </c>
       <c r="N13" t="n">
-        <v>9.710000677334346</v>
+        <v>9.673135441731091</v>
       </c>
       <c r="O13" t="n">
-        <v>3.116087398860043</v>
+        <v>3.110166465276592</v>
       </c>
       <c r="P13" t="n">
-        <v>400.1123982495133</v>
+        <v>400.1417065261072</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -21319,28 +21445,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2454985108425469</v>
+        <v>-0.2423287711927529</v>
       </c>
       <c r="J14" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K14" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1845564518742538</v>
+        <v>0.1824363033207558</v>
       </c>
       <c r="M14" t="n">
-        <v>3.010543897023421</v>
+        <v>3.007896815358202</v>
       </c>
       <c r="N14" t="n">
-        <v>14.15555758236408</v>
+        <v>14.10320870816784</v>
       </c>
       <c r="O14" t="n">
-        <v>3.762387218557398</v>
+        <v>3.755423905255949</v>
       </c>
       <c r="P14" t="n">
-        <v>402.1012464778463</v>
+        <v>402.0664862928884</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -21401,28 +21527,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.239041212502857</v>
+        <v>-0.2367323770393096</v>
       </c>
       <c r="J15" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K15" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2657501226957037</v>
+        <v>0.2643406688943634</v>
       </c>
       <c r="M15" t="n">
-        <v>2.075463614417169</v>
+        <v>2.074434202971075</v>
       </c>
       <c r="N15" t="n">
-        <v>8.392291548551558</v>
+        <v>8.358449421043209</v>
       </c>
       <c r="O15" t="n">
-        <v>2.896945209794545</v>
+        <v>2.891098307052738</v>
       </c>
       <c r="P15" t="n">
-        <v>401.4001344525124</v>
+        <v>401.3748155735651</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -21464,7 +21590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P308"/>
+  <dimension ref="A1:P310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46225,7 +46351,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>-35.27287680650941,174.0805924244868</t>
+          <t>-35.27284898119078,174.08070632344536</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -46305,11 +46431,7 @@
           <t>2025-12-07 22:11:45+00:00</t>
         </is>
       </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>-35.2729324825688,174.08036452096349</t>
-        </is>
-      </c>
+      <c r="B305" t="inlineStr"/>
       <c r="C305" t="inlineStr">
         <is>
           <t>-35.27368583591826,174.08039986737174</t>
@@ -46389,7 +46511,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>-35.27288573838847,174.0805558630094</t>
+          <t>-35.27283901964948,174.0807470994637</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -46471,7 +46593,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>-35.27292141431524,174.080409827746</t>
+          <t>-35.27283901964948,174.0807470994637</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -46553,7 +46675,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>-35.27292875025261,174.0803797988334</t>
+          <t>-35.27283901964948,174.0807470994637</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -46624,6 +46746,170 @@
       <c r="P308" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>-35.27283901964948,174.0807470994637</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>-35.27367776155603,174.08043842899434</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>-35.27438941317005,174.08064741487883</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>-35.27506446642047,174.08098357337795</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>-35.27561726368067,174.08150726915687</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>-35.27609550752614,174.08207721987304</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>-35.27654508757305,174.0827504353812</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>-35.276915670037155,174.08348519303905</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>-35.27726686459462,174.08421421248127</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>-35.27758762267682,174.08497930304617</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>-35.27784149119424,174.08580258845618</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>-35.278062751935245,174.08664161133223</t>
+        </is>
+      </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>-35.27819465083792,174.0875088294252</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>-35.2783494844163,174.08837995672235</t>
+        </is>
+      </c>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>-35.272806638111284,174.08087964779304</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>-35.27367776155603,174.08043842899434</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>-35.27438941317005,174.08064741487883</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>-35.27506077651681,174.0809957413774</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>-35.27561545060968,174.0815105520547</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>-35.27609306434239,174.08207998967694</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>-35.27653332714351,174.0827617235618</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>-35.27691340567035,174.08348699705408</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>-35.27726686459462,174.08421421248127</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>-35.27758762267682,174.08497930304617</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>-35.27784149119424,174.08580258845618</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>-35.278062751935245,174.08664161133223</t>
+        </is>
+      </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>-35.27818319782412,174.08751186682417</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>-35.27834223280357,174.08838171191624</t>
+        </is>
+      </c>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
